--- a/Config/Excel/skill/ability_segment.xlsx
+++ b/Config/Excel/skill/ability_segment.xlsx
@@ -29,12 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>effects</t>
+    <t>strikes</t>
+  </si>
+  <si>
+    <t>hit</t>
   </si>
   <si>
     <t>c</t>
@@ -47,6 +50,9 @@
   </si>
   <si>
     <t>int[]</t>
+  </si>
+  <si>
+    <t>命中判定</t>
   </si>
   <si>
     <t>130000,130001</t>
@@ -665,11 +671,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -992,114 +1001,127 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="14.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="35.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+    <row r="4" spans="1:4">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1">
         <v>120000</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1">
         <v>120001</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1">
         <v>120002</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1">
         <v>120003</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1">
         <v>120004</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="1">
         <v>120005</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="1">
         <v>120006</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="1">
         <v>120007</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="1">
         <v>120008</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="1">
         <v>120009</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="1">
         <v>120010</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="1">
         <v>120011</v>
       </c>

--- a/Config/Excel/skill/ability_segment.xlsx
+++ b/Config/Excel/skill/ability_segment.xlsx
@@ -29,15 +29,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>strikes</t>
-  </si>
-  <si>
-    <t>hit</t>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>fixedEffects</t>
+  </si>
+  <si>
+    <t>hitEffects</t>
+  </si>
+  <si>
+    <t>casterEffects</t>
   </si>
   <si>
     <t>c</t>
@@ -52,7 +58,19 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>命中判定</t>
+    <t>范围（1、所有目标；2、随机目标）</t>
+  </si>
+  <si>
+    <t>固定效果</t>
+  </si>
+  <si>
+    <t>命中生效</t>
+  </si>
+  <si>
+    <t>对释放者生效</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>130000,130001</t>
@@ -1001,127 +1019,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="35.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="30.375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>120000</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>120001</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>120002</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>120003</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>120004</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>120005</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>120006</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>120007</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>120008</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>120009</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>120010</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>120011</v>
       </c>

--- a/Config/Excel/skill/ability_segment.xlsx
+++ b/Config/Excel/skill/ability_segment.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\demo\Project001\Config\Excel\skill\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -29,21 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>Range</t>
-  </si>
-  <si>
-    <t>fixedEffects</t>
-  </si>
-  <si>
-    <t>hitEffects</t>
-  </si>
-  <si>
-    <t>casterEffects</t>
+    <t>strikes</t>
   </si>
   <si>
     <t>c</t>
@@ -58,22 +54,13 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>范围（1、所有目标；2、随机目标）</t>
+    <t>技能段的击中点</t>
   </si>
   <si>
-    <t>固定效果</t>
+    <t>130000</t>
   </si>
   <si>
-    <t>命中生效</t>
-  </si>
-  <si>
-    <t>对释放者生效</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>130000,130001</t>
+    <t>130001</t>
   </si>
 </sst>
 </file>
@@ -689,14 +676,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1019,162 +1003,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="14.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="14.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="30.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="35.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="1">
         <v>120000</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="1">
         <v>120001</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="1">
         <v>120002</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:3">
       <c r="A8" s="1">
         <v>120003</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:3">
       <c r="A9" s="1">
         <v>120004</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:3">
       <c r="A10" s="1">
         <v>120005</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:3">
       <c r="A11" s="1">
         <v>120006</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:3">
       <c r="A12" s="1">
         <v>120007</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:3">
       <c r="A13" s="1">
         <v>120008</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:3">
       <c r="A14" s="1">
         <v>120009</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:3">
       <c r="A15" s="1">
         <v>120010</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:3">
       <c r="A16" s="1">
         <v>120011</v>
       </c>
